--- a/smart_travel_planner_test_case_report.xlsx
+++ b/smart_travel_planner_test_case_report.xlsx
@@ -520,43 +520,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Module / Component</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Test Title</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
     <row r="3" ht="10" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="n"/>
@@ -4379,43 +4343,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Test Case ID</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Module / Component</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Test Title</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Preconditions</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Test Steps</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
+    <row r="2"/>
     <row r="3" ht="10" customHeight="1"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="2" t="n"/>

--- a/smart_travel_planner_test_case_report.xlsx
+++ b/smart_travel_planner_test_case_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Web (Selenium Tests)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mobile App (Appium Tests)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Web (Selenium Tests)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Mobile App (Appium Tests)" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
